--- a/data/trending_integrated_20261012_15.xlsx
+++ b/data/trending_integrated_20261012_15.xlsx
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19977802900</v>
+        <v>19984603460</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>132329805860</v>
+        <v>132366248300</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13530</v>
+        <v>13390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+21.45%</t>
+          <t>'+20.20%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F4" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G4" t="n">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>183398308005</v>
+        <v>186093329175</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1599</v>
+        <v>1586</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+15.28%</t>
+          <t>'+14.35%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>11685436737</v>
+        <v>11781756956</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7560</v>
+        <v>7520</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.78%</t>
+          <t>'+6.21%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-1.1</v>
       </c>
       <c r="E6" t="n">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="F6" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G6" t="n">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="H6" t="n">
         <v>1.99</v>
@@ -978,7 +978,7 @@
         <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>125294344035</v>
+        <v>126700109905</v>
       </c>
       <c r="P6" t="n">
         <v>23500</v>
@@ -1023,31 +1023,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>녹십자엠에스</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3730</v>
+        <v>2305</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.13%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-1.19</v>
+        <v>0.16</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F7" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>124</v>
+        <v>158</v>
       </c>
       <c r="H7" t="n">
-        <v>0.78</v>
+        <v>1.48</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,38 +1055,38 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3735</v>
+        <v>2305</v>
       </c>
       <c r="K7" t="n">
-        <v>3660</v>
+        <v>2430</v>
       </c>
       <c r="L7" t="n">
-        <v>4300</v>
+        <v>2445</v>
       </c>
       <c r="M7" t="n">
-        <v>3660</v>
+        <v>2210</v>
       </c>
       <c r="N7" t="n">
-        <v>1.97</v>
+        <v>1.32</v>
       </c>
       <c r="O7" t="n">
-        <v>73313169391</v>
+        <v>35131237545</v>
       </c>
       <c r="P7" t="n">
-        <v>6660</v>
+        <v>2465</v>
       </c>
       <c r="Q7" t="n">
-        <v>2200</v>
+        <v>865</v>
       </c>
       <c r="R7" t="n">
-        <v>1000</v>
+        <v>-497000</v>
       </c>
       <c r="S7" t="n">
-        <v>-82000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>러시아 방역 강화 관련 소식 언급, 단기 급등 후 차익 실현 가능성.</t>
+          <t>대표이사 및 회사 운영에 대한 비판과 함께 주가 상승에 대한 기대감 표출. IR 인터뷰 게재 사실 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['러시아 방역', '차익 실현']</t>
+          <t>['대표이사 비판', '주가 상승 기대', 'IR 인터뷰']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>142280</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>녹십자엠에스</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2290</v>
+        <v>3700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.65%</t>
+          <t>'-0.94%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.16</v>
+        <v>-1.19</v>
       </c>
       <c r="E8" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="H8" t="n">
-        <v>1.48</v>
+        <v>0.78</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>2305</v>
+        <v>3735</v>
       </c>
       <c r="K8" t="n">
-        <v>2430</v>
+        <v>3660</v>
       </c>
       <c r="L8" t="n">
-        <v>2445</v>
+        <v>4300</v>
       </c>
       <c r="M8" t="n">
-        <v>2210</v>
+        <v>3660</v>
       </c>
       <c r="N8" t="n">
-        <v>1.32</v>
+        <v>1.97</v>
       </c>
       <c r="O8" t="n">
-        <v>32788666795</v>
+        <v>73586890421</v>
       </c>
       <c r="P8" t="n">
-        <v>2465</v>
+        <v>6660</v>
       </c>
       <c r="Q8" t="n">
-        <v>865</v>
+        <v>2200</v>
       </c>
       <c r="R8" t="n">
-        <v>-497000</v>
+        <v>1000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-82000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대표이사 및 회사 운영에 대한 비판과 함께 주가 상승에 대한 기대감 표출. IR 인터뷰 게재 사실 언급.</t>
+          <t>러시아 방역 강화 관련 소식 언급, 단기 급등 후 차익 실현 가능성.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['대표이사 비판', '주가 상승 기대', 'IR 인터뷰']</t>
+          <t>['러시아 방역', '차익 실현']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>142280</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44550</v>
+        <v>44450</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.41%</t>
+          <t>'-2.63%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F9" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G9" t="n">
-        <v>3074</v>
+        <v>3108</v>
       </c>
       <c r="H9" t="n">
         <v>13.33</v>
@@ -1254,7 +1254,7 @@
         <v>13.39</v>
       </c>
       <c r="O9" t="n">
-        <v>39382751300</v>
+        <v>40223354775</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13570</v>
+        <v>13540</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.44%</t>
+          <t>'-2.66%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>287</v>
       </c>
       <c r="F10" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G10" t="n">
-        <v>572</v>
+        <v>585</v>
       </c>
       <c r="H10" t="n">
         <v>0.21</v>
@@ -1346,7 +1346,7 @@
         <v>0.09</v>
       </c>
       <c r="O10" t="n">
-        <v>159836033285</v>
+        <v>160838779135</v>
       </c>
       <c r="P10" t="n">
         <v>28700</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16090</v>
+        <v>16030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.48%</t>
+          <t>'-3.84%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G11" t="n">
-        <v>860</v>
+        <v>867</v>
       </c>
       <c r="H11" t="n">
         <v>9.470000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.460000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>63249841905</v>
+        <v>64520351735</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1612000</v>
+        <v>251000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.10%</t>
+          <t>'-4.20%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E12" t="n">
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>503</v>
+        <v>548</v>
       </c>
       <c r="G12" t="n">
-        <v>1954</v>
+        <v>2058</v>
       </c>
       <c r="H12" t="n">
-        <v>49.52</v>
+        <v>46.35</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1681000</v>
+        <v>262000</v>
       </c>
       <c r="K12" t="n">
-        <v>1640000</v>
+        <v>260000</v>
       </c>
       <c r="L12" t="n">
-        <v>1653000</v>
+        <v>262500</v>
       </c>
       <c r="M12" t="n">
-        <v>1605000</v>
+        <v>249500</v>
       </c>
       <c r="N12" t="n">
-        <v>49.59</v>
+        <v>46.38</v>
       </c>
       <c r="O12" t="n">
-        <v>4036076456500</v>
+        <v>3869520919000</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R12" t="n">
-        <v>-259000</v>
+        <v>-1572000</v>
       </c>
       <c r="S12" t="n">
-        <v>88000</v>
+        <v>-583000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>증권사 목표가 하향 및 정치적 요인으로 인한 증시 붕괴 우려. 주가 조작 및 공매도 관련 불만.</t>
+          <t>정부 정책 및 시장 상황에 대한 부정적 인식. 개인 투자자들의 불만 표출.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['목표가', '증시', '공매도']</t>
+          <t>['정부 정책', '시장 상황', '개인 투자자']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>251000</v>
+        <v>1610000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.20%</t>
+          <t>'-4.22%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>547</v>
+        <v>496</v>
       </c>
       <c r="G13" t="n">
-        <v>1960</v>
+        <v>1906</v>
       </c>
       <c r="H13" t="n">
-        <v>46.35</v>
+        <v>49.52</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,47 +1607,47 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>262000</v>
+        <v>1681000</v>
       </c>
       <c r="K13" t="n">
-        <v>260000</v>
+        <v>1640000</v>
       </c>
       <c r="L13" t="n">
-        <v>262500</v>
+        <v>1653000</v>
       </c>
       <c r="M13" t="n">
-        <v>249500</v>
+        <v>1605000</v>
       </c>
       <c r="N13" t="n">
-        <v>46.38</v>
+        <v>49.59</v>
       </c>
       <c r="O13" t="n">
-        <v>3783628341750</v>
+        <v>4120616292000</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>90200</v>
+        <v>403000</v>
       </c>
       <c r="R13" t="n">
-        <v>-1572000</v>
+        <v>-259000</v>
       </c>
       <c r="S13" t="n">
-        <v>-583000</v>
+        <v>88000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정치적 요인에 따른 증시 불안감과 삼성전자 주가 하락 우려 제기. 공매도 중지 요구.</t>
+          <t>정부 정책 실패 및 증시 상황에 대한 강한 불만. 주가 폭락에 대한 비판.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정치', '공매도', '증시']</t>
+          <t>['정부 정책', '증시 상황', '주가 폭락']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1671,24 +1671,24 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7800</v>
+        <v>7780</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.41%</t>
+          <t>'-4.66%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F14" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G14" t="n">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="H14" t="n">
         <v>26.37</v>
@@ -1714,7 +1714,7 @@
         <v>26.38</v>
       </c>
       <c r="O14" t="n">
-        <v>30096920285</v>
+        <v>30596859285</v>
       </c>
       <c r="P14" t="n">
         <v>17950</v>
@@ -1759,70 +1759,70 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15800</v>
+        <v>17950</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-6.89%</t>
+          <t>'-4.83%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.6</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="F15" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="G15" t="n">
-        <v>582</v>
+        <v>425</v>
       </c>
       <c r="H15" t="n">
-        <v>3.37</v>
+        <v>27.61</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>16970</v>
+        <v>18860</v>
       </c>
       <c r="K15" t="n">
-        <v>17030</v>
+        <v>18690</v>
       </c>
       <c r="L15" t="n">
-        <v>17400</v>
+        <v>18760</v>
       </c>
       <c r="M15" t="n">
-        <v>15650</v>
+        <v>17950</v>
       </c>
       <c r="N15" t="n">
-        <v>3.97</v>
+        <v>27.68</v>
       </c>
       <c r="O15" t="n">
-        <v>81926191545</v>
+        <v>60187347340</v>
       </c>
       <c r="P15" t="n">
-        <v>31500</v>
+        <v>35350</v>
       </c>
       <c r="Q15" t="n">
-        <v>1272</v>
+        <v>17950</v>
       </c>
       <c r="R15" t="n">
-        <v>68000</v>
+        <v>93000</v>
       </c>
       <c r="S15" t="n">
-        <v>-56000</v>
+        <v>23000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>3분기 실적 서프라이즈 발표와 함께 광통신 테마 및 AI 관련 긍정적 전망. 유튜버 언급.</t>
+          <t>실적 호조에도 불구하고 주가 하락 및 52주 신저가 기록. 공매도 관련 불만과 조선업 전반의 부정적 전망.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['실적', '광통신', 'AI']</t>
+          <t>['실적', '공매도', '신저가']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,77 +1844,77 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18050</v>
+        <v>15710</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-7.48%</t>
+          <t>'-7.42%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.6</v>
       </c>
       <c r="E16" t="n">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="F16" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G16" t="n">
-        <v>420</v>
+        <v>582</v>
       </c>
       <c r="H16" t="n">
-        <v>27.61</v>
+        <v>3.37</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>19510</v>
+        <v>16970</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>17030</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>17400</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>15650</v>
       </c>
       <c r="N16" t="n">
-        <v>27.68</v>
+        <v>3.97</v>
       </c>
       <c r="O16" t="n">
-        <v>58219000000</v>
+        <v>83617753860</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>31500</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1272</v>
       </c>
       <c r="R16" t="n">
-        <v>93000</v>
+        <v>68000</v>
       </c>
       <c r="S16" t="n">
-        <v>23000</v>
+        <v>-56000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>실적 호조에도 불구하고 주가 하락 및 52주 신저가 기록. 공매도 관련 불만과 조선업 전반의 부정적 전망.</t>
+          <t>3분기 실적 서프라이즈 발표와 함께 광통신 테마 및 AI 관련 긍정적 전망. 유튜버 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '신저가']</t>
+          <t>['실적', '광통신', 'AI']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,77 +1936,77 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10440</v>
+        <v>25650</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-7.94%</t>
+          <t>'-8.72%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.03</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="G17" t="n">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="H17" t="n">
-        <v>0.41</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>11340</v>
+        <v>28100</v>
       </c>
       <c r="K17" t="n">
-        <v>11340</v>
+        <v>27600</v>
       </c>
       <c r="L17" t="n">
-        <v>12470</v>
+        <v>27800</v>
       </c>
       <c r="M17" t="n">
-        <v>10430</v>
+        <v>25600</v>
       </c>
       <c r="N17" t="n">
-        <v>0.44</v>
+        <v>10.02</v>
       </c>
       <c r="O17" t="n">
-        <v>31442267600</v>
+        <v>66903924150</v>
       </c>
       <c r="P17" t="n">
-        <v>29750</v>
+        <v>75900</v>
       </c>
       <c r="Q17" t="n">
-        <v>10430</v>
+        <v>15960</v>
       </c>
       <c r="R17" t="n">
-        <v>8000</v>
+        <v>-57000</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-7000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
+          <t>경영진의 무능력 지적, LS 기술유출 타격 언급. 실적 개선 근거 부족 및 투매 우려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,11 +2015,11 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
+          <t>['경영진 부진', '기술유출', '실적 우려']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,77 +2028,77 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>486510</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25800</v>
+        <v>10350</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.19%</t>
+          <t>'-8.73%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G18" t="n">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="H18" t="n">
-        <v>9.460000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>28100</v>
+        <v>11340</v>
       </c>
       <c r="K18" t="n">
-        <v>27600</v>
+        <v>11340</v>
       </c>
       <c r="L18" t="n">
-        <v>27800</v>
+        <v>12470</v>
       </c>
       <c r="M18" t="n">
-        <v>25600</v>
+        <v>10310</v>
       </c>
       <c r="N18" t="n">
-        <v>10.02</v>
+        <v>0.44</v>
       </c>
       <c r="O18" t="n">
-        <v>65253452200</v>
+        <v>31863179060</v>
       </c>
       <c r="P18" t="n">
-        <v>75900</v>
+        <v>29750</v>
       </c>
       <c r="Q18" t="n">
-        <v>15960</v>
+        <v>10310</v>
       </c>
       <c r="R18" t="n">
-        <v>-57000</v>
+        <v>8000</v>
       </c>
       <c r="S18" t="n">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>경영진의 무능력 지적, LS 기술유출 타격 언급. 실적 개선 근거 부족 및 투매 우려.</t>
+          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
@@ -2107,11 +2107,11 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['경영진 부진', '기술유출', '실적 우려']</t>
+          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3820</v>
+        <v>3840</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-10.54%</t>
+          <t>'-10.07%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2174,7 +2174,7 @@
         <v>4.46</v>
       </c>
       <c r="O19" t="n">
-        <v>19253109925</v>
+        <v>19463029271</v>
       </c>
       <c r="P19" t="n">
         <v>5470</v>

--- a/data/trending_integrated_20261012_15.xlsx
+++ b/data/trending_integrated_20261012_15.xlsx
@@ -584,7 +584,7 @@
         <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19984603460</v>
+        <v>19991667660</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -676,7 +676,7 @@
         <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>132366248300</v>
+        <v>132394543220</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13390</v>
+        <v>13400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+20.20%</t>
+          <t>'+20.29%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F4" t="n">
         <v>90</v>
       </c>
       <c r="G4" t="n">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>186093329175</v>
+        <v>188044383275</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>금호건설의 상승 기대감과 함께 외인 매도 동향 언급. 단기 상승 패턴 전망.</t>
+          <t>금호건설의 단기 급등에 대한 기대감. 일부 긍정적 흐름 속 상승 패턴 지속 전망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['상승', '외인', '패턴']</t>
+          <t>['금호건설', '상승 패턴', '기대감']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.35%</t>
+          <t>'+13.77%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F5" t="n">
         <v>32</v>
       </c>
       <c r="G5" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>11781756956</v>
+        <v>11877372223</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7520</v>
+        <v>7390</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+6.21%</t>
+          <t>'+4.38%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-1.1</v>
       </c>
       <c r="E6" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F6" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G6" t="n">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="H6" t="n">
         <v>1.99</v>
@@ -978,7 +978,7 @@
         <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>126700109905</v>
+        <v>128179902015</v>
       </c>
       <c r="P6" t="n">
         <v>23500</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2305</v>
+        <v>2295</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.43%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>0.16</v>
       </c>
       <c r="E7" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="H7" t="n">
         <v>1.48</v>
@@ -1070,7 +1070,7 @@
         <v>1.32</v>
       </c>
       <c r="O7" t="n">
-        <v>35131237545</v>
+        <v>35754950915</v>
       </c>
       <c r="P7" t="n">
         <v>2465</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3700</v>
+        <v>3690</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.94%</t>
+          <t>'-1.20%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-1.19</v>
       </c>
       <c r="E8" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G8" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H8" t="n">
         <v>0.78</v>
@@ -1162,7 +1162,7 @@
         <v>1.97</v>
       </c>
       <c r="O8" t="n">
-        <v>73586890421</v>
+        <v>74008391331</v>
       </c>
       <c r="P8" t="n">
         <v>6660</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44450</v>
+        <v>44350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.63%</t>
+          <t>'-2.85%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F9" t="n">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G9" t="n">
-        <v>3108</v>
+        <v>3153</v>
       </c>
       <c r="H9" t="n">
         <v>13.33</v>
@@ -1254,7 +1254,7 @@
         <v>13.39</v>
       </c>
       <c r="O9" t="n">
-        <v>40223354775</v>
+        <v>40855305875</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>FDA 리보세라닙 재승인 서류 제출 공시. 긍정적인 뉴스에 따른 주가 상승 기대감.</t>
+          <t>HLB, 리보세라닙 간암 1차 치료제 FDA 재승인 서류 제출 완료. 빠른 재신청 절차와 연말 30만 목표 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA', '리보세라닙', '공시']</t>
+          <t>['HLB', 'FDA 재승인', '리보세라닙']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13540</v>
+        <v>13430</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.66%</t>
+          <t>'-3.45%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.12</v>
       </c>
       <c r="E10" t="n">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="F10" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G10" t="n">
-        <v>585</v>
+        <v>600</v>
       </c>
       <c r="H10" t="n">
         <v>0.21</v>
@@ -1346,7 +1346,7 @@
         <v>0.09</v>
       </c>
       <c r="O10" t="n">
-        <v>160838779135</v>
+        <v>162073139530</v>
       </c>
       <c r="P10" t="n">
         <v>28700</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16030</v>
+        <v>16050</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.84%</t>
+          <t>'-3.72%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="F11" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G11" t="n">
-        <v>867</v>
+        <v>873</v>
       </c>
       <c r="H11" t="n">
         <v>9.470000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.460000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>64520351735</v>
+        <v>65750633840</v>
       </c>
       <c r="P11" t="n">
         <v>40350</v>
@@ -1483,31 +1483,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>251000</v>
+        <v>1613000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.20%</t>
+          <t>'-4.05%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>548</v>
+        <v>491</v>
       </c>
       <c r="G12" t="n">
-        <v>2058</v>
+        <v>1904</v>
       </c>
       <c r="H12" t="n">
-        <v>46.35</v>
+        <v>49.52</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>262000</v>
+        <v>1681000</v>
       </c>
       <c r="K12" t="n">
-        <v>260000</v>
+        <v>1640000</v>
       </c>
       <c r="L12" t="n">
-        <v>262500</v>
+        <v>1653000</v>
       </c>
       <c r="M12" t="n">
-        <v>249500</v>
+        <v>1605000</v>
       </c>
       <c r="N12" t="n">
-        <v>46.38</v>
+        <v>49.59</v>
       </c>
       <c r="O12" t="n">
-        <v>3869520919000</v>
+        <v>4259701604500</v>
       </c>
       <c r="P12" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q12" t="n">
-        <v>90200</v>
+        <v>403000</v>
       </c>
       <c r="R12" t="n">
-        <v>-1572000</v>
+        <v>-259000</v>
       </c>
       <c r="S12" t="n">
-        <v>-583000</v>
+        <v>88000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정부 정책 및 시장 상황에 대한 부정적 인식. 개인 투자자들의 불만 표출.</t>
+          <t>정부 정책 및 시장 시스템 문제로 인한 SK하이닉스 주가 폭락 우려. 세계적 기업 실적 대비 주가 부진.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['정부 정책', '시장 상황', '개인 투자자']</t>
+          <t>['정부 정책', '주가 폭락', '실적 부진']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1610000</v>
+        <v>251000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.22%</t>
+          <t>'-4.20%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E13" t="n">
         <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>496</v>
+        <v>558</v>
       </c>
       <c r="G13" t="n">
-        <v>1906</v>
+        <v>2027</v>
       </c>
       <c r="H13" t="n">
-        <v>49.52</v>
+        <v>46.35</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,38 +1607,38 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1681000</v>
+        <v>262000</v>
       </c>
       <c r="K13" t="n">
-        <v>1640000</v>
+        <v>260000</v>
       </c>
       <c r="L13" t="n">
-        <v>1653000</v>
+        <v>262500</v>
       </c>
       <c r="M13" t="n">
-        <v>1605000</v>
+        <v>249500</v>
       </c>
       <c r="N13" t="n">
-        <v>49.59</v>
+        <v>46.38</v>
       </c>
       <c r="O13" t="n">
-        <v>4120616292000</v>
+        <v>3949715047750</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q13" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R13" t="n">
-        <v>-259000</v>
+        <v>-1572000</v>
       </c>
       <c r="S13" t="n">
-        <v>88000</v>
+        <v>-583000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정부 정책 실패 및 증시 상황에 대한 강한 불만. 주가 폭락에 대한 비판.</t>
+          <t>정부 정책 실패 및 시스템 문제로 인한 증시 전반의 불안 심리. 삼성전자 주가 하락에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정부 정책', '증시 상황', '주가 폭락']</t>
+          <t>['정부 정책', '증시 불안', '주가 하락']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7780</v>
+        <v>17970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.66%</t>
+          <t>'-4.72%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>205</v>
+        <v>152</v>
       </c>
       <c r="F14" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="G14" t="n">
-        <v>826</v>
+        <v>440</v>
       </c>
       <c r="H14" t="n">
-        <v>26.37</v>
+        <v>27.61</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8160</v>
+        <v>18860</v>
       </c>
       <c r="K14" t="n">
-        <v>8070</v>
+        <v>18690</v>
       </c>
       <c r="L14" t="n">
-        <v>8110</v>
+        <v>18760</v>
       </c>
       <c r="M14" t="n">
-        <v>7700</v>
+        <v>17910</v>
       </c>
       <c r="N14" t="n">
-        <v>26.38</v>
+        <v>27.68</v>
       </c>
       <c r="O14" t="n">
-        <v>30596859285</v>
+        <v>62769427650</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>35350</v>
       </c>
       <c r="Q14" t="n">
-        <v>7700</v>
+        <v>17910</v>
       </c>
       <c r="R14" t="n">
-        <v>-1233000</v>
+        <v>93000</v>
       </c>
       <c r="S14" t="n">
-        <v>12000</v>
+        <v>23000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>LG디스플레이 실적 부진 및 기업 가치 하락 전망, 투자자 이탈.</t>
+          <t>실적 호조에도 불구하고 주가 하락 및 52주 신저가 기록. 공매도 관련 불만과 조선업 전반의 부정적 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적 부진', '기업 가치 하락']</t>
+          <t>['실적', '공매도', '신저가']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B15" t="n">
+        <v>7770</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'-4.78%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E15" t="n">
+        <v>208</v>
+      </c>
+      <c r="F15" t="n">
+        <v>94</v>
+      </c>
+      <c r="G15" t="n">
+        <v>827</v>
+      </c>
+      <c r="H15" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>8160</v>
+      </c>
+      <c r="K15" t="n">
+        <v>8070</v>
+      </c>
+      <c r="L15" t="n">
+        <v>8110</v>
+      </c>
+      <c r="M15" t="n">
+        <v>7700</v>
+      </c>
+      <c r="N15" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="O15" t="n">
+        <v>31216704715</v>
+      </c>
+      <c r="P15" t="n">
         <v>17950</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>'-4.83%</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="E15" t="n">
-        <v>145</v>
-      </c>
-      <c r="F15" t="n">
-        <v>76</v>
-      </c>
-      <c r="G15" t="n">
-        <v>425</v>
-      </c>
-      <c r="H15" t="n">
-        <v>27.61</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>MarketType.KOSPI</t>
-        </is>
-      </c>
-      <c r="J15" t="n">
-        <v>18860</v>
-      </c>
-      <c r="K15" t="n">
-        <v>18690</v>
-      </c>
-      <c r="L15" t="n">
-        <v>18760</v>
-      </c>
-      <c r="M15" t="n">
-        <v>17950</v>
-      </c>
-      <c r="N15" t="n">
-        <v>27.68</v>
-      </c>
-      <c r="O15" t="n">
-        <v>60187347340</v>
-      </c>
-      <c r="P15" t="n">
-        <v>35350</v>
-      </c>
       <c r="Q15" t="n">
-        <v>17950</v>
+        <v>7700</v>
       </c>
       <c r="R15" t="n">
-        <v>93000</v>
+        <v>-1233000</v>
       </c>
       <c r="S15" t="n">
-        <v>23000</v>
+        <v>12000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>실적 호조에도 불구하고 주가 하락 및 52주 신저가 기록. 공매도 관련 불만과 조선업 전반의 부정적 전망.</t>
+          <t>LG디스플레이 실적 부진 및 기업 가치 하락 전망, 투자자 이탈.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '신저가']</t>
+          <t>['실적 부진', '기업 가치 하락']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15710</v>
+        <v>15730</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-7.42%</t>
+          <t>'-7.31%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.6</v>
       </c>
       <c r="E16" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F16" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G16" t="n">
-        <v>582</v>
+        <v>603</v>
       </c>
       <c r="H16" t="n">
         <v>3.37</v>
@@ -1898,7 +1898,7 @@
         <v>3.97</v>
       </c>
       <c r="O16" t="n">
-        <v>83617753860</v>
+        <v>85067594480</v>
       </c>
       <c r="P16" t="n">
         <v>31500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>3분기 실적 서프라이즈 발표와 함께 광통신 테마 및 AI 관련 긍정적 전망. 유튜버 언급.</t>
+          <t>AI 및 광통신 테마 확산 속 대한광통신 3분기 어닝 서프라이즈 기록. 공매도 규제 논의.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['실적', '광통신', 'AI']</t>
+          <t>['대한광통신', '어닝 서프라이즈', 'AI 테마']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25650</v>
+        <v>25750</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-8.72%</t>
+          <t>'-8.36%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G17" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="H17" t="n">
         <v>9.460000000000001</v>
@@ -1990,7 +1990,7 @@
         <v>10.02</v>
       </c>
       <c r="O17" t="n">
-        <v>66903924150</v>
+        <v>68487984000</v>
       </c>
       <c r="P17" t="n">
         <v>75900</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10350</v>
+        <v>10390</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.73%</t>
+          <t>'-8.38%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="F18" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G18" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="H18" t="n">
         <v>0.41</v>
@@ -2082,7 +2082,7 @@
         <v>0.44</v>
       </c>
       <c r="O18" t="n">
-        <v>31863179060</v>
+        <v>32113397130</v>
       </c>
       <c r="P18" t="n">
         <v>29750</v>
@@ -2131,18 +2131,18 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3840</v>
+        <v>3845</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-10.07%</t>
+          <t>'-9.95%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-2.94</v>
       </c>
       <c r="E19" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F19" t="n">
         <v>32</v>
@@ -2174,7 +2174,7 @@
         <v>4.46</v>
       </c>
       <c r="O19" t="n">
-        <v>19463029271</v>
+        <v>19535483868</v>
       </c>
       <c r="P19" t="n">
         <v>5470</v>

--- a/data/trending_integrated_20261012_15.xlsx
+++ b/data/trending_integrated_20261012_15.xlsx
@@ -578,13 +578,13 @@
         <v>0.61</v>
       </c>
       <c r="E2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F2" t="n">
         <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19991667660</v>
+        <v>19991877220</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>132394543220</v>
+        <v>132412598390</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -762,13 +762,13 @@
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F4" t="n">
         <v>90</v>
       </c>
       <c r="G4" t="n">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>188044383275</v>
+        <v>188731428075</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>금호건설의 단기 급등에 대한 기대감. 일부 긍정적 흐름 속 상승 패턴 지속 전망.</t>
+          <t>긍정적 상승 흐름 및 잠재력에 대한 기대감 표출. 의도적인 주가 억제 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['금호건설', '상승 패턴', '기대감']</t>
+          <t>['상승 패턴', '주가 억제', '잠재력']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>11877372223</v>
+        <v>11917846345</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7390</v>
+        <v>7410</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+4.38%</t>
+          <t>'+4.66%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-1.1</v>
       </c>
       <c r="E6" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F6" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G6" t="n">
-        <v>675</v>
+        <v>689</v>
       </c>
       <c r="H6" t="n">
         <v>1.99</v>
@@ -978,7 +978,7 @@
         <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>128179902015</v>
+        <v>128837865555</v>
       </c>
       <c r="P6" t="n">
         <v>23500</v>
@@ -1038,7 +1038,7 @@
         <v>0.16</v>
       </c>
       <c r="E7" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="n">
         <v>47</v>
@@ -1070,7 +1070,7 @@
         <v>1.32</v>
       </c>
       <c r="O7" t="n">
-        <v>35754950915</v>
+        <v>36133860005</v>
       </c>
       <c r="P7" t="n">
         <v>2465</v>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3690</v>
+        <v>3710</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.20%</t>
+          <t>'-0.67%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-1.19</v>
       </c>
       <c r="E8" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F8" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G8" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H8" t="n">
         <v>0.78</v>
@@ -1162,7 +1162,7 @@
         <v>1.97</v>
       </c>
       <c r="O8" t="n">
-        <v>74008391331</v>
+        <v>74188177931</v>
       </c>
       <c r="P8" t="n">
         <v>6660</v>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44350</v>
+        <v>44400</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.85%</t>
+          <t>'-2.74%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F9" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G9" t="n">
-        <v>3153</v>
+        <v>3169</v>
       </c>
       <c r="H9" t="n">
         <v>13.33</v>
@@ -1254,7 +1254,7 @@
         <v>13.39</v>
       </c>
       <c r="O9" t="n">
-        <v>40855305875</v>
+        <v>41677505075</v>
       </c>
       <c r="P9" t="n">
         <v>69200</v>
@@ -1299,70 +1299,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13430</v>
+        <v>16090</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.45%</t>
+          <t>'-3.48%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.12</v>
+        <v>0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>295</v>
+        <v>226</v>
       </c>
       <c r="F10" t="n">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="G10" t="n">
-        <v>600</v>
+        <v>901</v>
       </c>
       <c r="H10" t="n">
-        <v>0.21</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13910</v>
+        <v>16670</v>
       </c>
       <c r="K10" t="n">
-        <v>13350</v>
+        <v>16500</v>
       </c>
       <c r="L10" t="n">
-        <v>15790</v>
+        <v>16870</v>
       </c>
       <c r="M10" t="n">
-        <v>13350</v>
+        <v>15950</v>
       </c>
       <c r="N10" t="n">
-        <v>0.09</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>162073139530</v>
+        <v>66968904280</v>
       </c>
       <c r="P10" t="n">
-        <v>28700</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>11600</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>-15000</v>
+        <v>624000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-94000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>운전이 더럽다는 평가와 함께 개미 털기 및 대차 공매도 관련 우려 제기. 주가 하락 가능성 언급.</t>
+          <t>계속되는 주가 하락에 대한 불만과 특정 세력(모간이, 대차 해지 세력)에 대한 비난.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,11 +1371,11 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', '대차', '개미']</t>
+          <t>['대차', '주가', '뱅크런']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,77 +1384,77 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16050</v>
+        <v>13410</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.72%</t>
+          <t>'-3.59%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="E11" t="n">
-        <v>217</v>
+        <v>303</v>
       </c>
       <c r="F11" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="G11" t="n">
-        <v>873</v>
+        <v>635</v>
       </c>
       <c r="H11" t="n">
-        <v>9.470000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16670</v>
+        <v>13910</v>
       </c>
       <c r="K11" t="n">
-        <v>16500</v>
+        <v>13350</v>
       </c>
       <c r="L11" t="n">
-        <v>16870</v>
+        <v>15790</v>
       </c>
       <c r="M11" t="n">
-        <v>15950</v>
+        <v>13350</v>
       </c>
       <c r="N11" t="n">
-        <v>9.460000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="O11" t="n">
-        <v>65750633840</v>
+        <v>162469029550</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>28700</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>11600</v>
       </c>
       <c r="R11" t="n">
-        <v>624000</v>
+        <v>-15000</v>
       </c>
       <c r="S11" t="n">
-        <v>-94000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>계속되는 주가 하락에 대한 불만과 특정 세력(모간이, 대차 해지 세력)에 대한 비난.</t>
+          <t>주가 운전 방식에 대한 불만과 함께 추가 하락 가능성 제기. 보호예수 해제 및 기관 매매 동향 주시.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['대차', '주가', '뱅크런']</t>
+          <t>['주가 운전', '보호예수', '기관 매매']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1613000</v>
+        <v>250500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-4.05%</t>
+          <t>'-4.39%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="E12" t="n">
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>491</v>
+        <v>554</v>
       </c>
       <c r="G12" t="n">
-        <v>1904</v>
+        <v>2003</v>
       </c>
       <c r="H12" t="n">
-        <v>49.52</v>
+        <v>46.35</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1681000</v>
+        <v>262000</v>
       </c>
       <c r="K12" t="n">
-        <v>1640000</v>
+        <v>260000</v>
       </c>
       <c r="L12" t="n">
-        <v>1653000</v>
+        <v>262500</v>
       </c>
       <c r="M12" t="n">
-        <v>1605000</v>
+        <v>249500</v>
       </c>
       <c r="N12" t="n">
-        <v>49.59</v>
+        <v>46.38</v>
       </c>
       <c r="O12" t="n">
-        <v>4259701604500</v>
+        <v>4361609191750</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>374500</v>
       </c>
       <c r="Q12" t="n">
-        <v>403000</v>
+        <v>90200</v>
       </c>
       <c r="R12" t="n">
-        <v>-259000</v>
+        <v>-1572000</v>
       </c>
       <c r="S12" t="n">
-        <v>88000</v>
+        <v>-583000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정부 정책 및 시장 시스템 문제로 인한 SK하이닉스 주가 폭락 우려. 세계적 기업 실적 대비 주가 부진.</t>
+          <t>정부 정책 및 거시 경제 상황에 대한 불만 고조. 시장 시스템 및 한국 증시의 이상 징후 제기.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['정부 정책', '주가 폭락', '실적 부진']</t>
+          <t>['정부 정책', '거시 경제', '한국 증시']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>251000</v>
+        <v>18010</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-4.20%</t>
+          <t>'-4.51%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>153</v>
       </c>
       <c r="F13" t="n">
-        <v>558</v>
+        <v>78</v>
       </c>
       <c r="G13" t="n">
-        <v>2027</v>
+        <v>451</v>
       </c>
       <c r="H13" t="n">
-        <v>46.35</v>
+        <v>27.61</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>262000</v>
+        <v>18860</v>
       </c>
       <c r="K13" t="n">
-        <v>260000</v>
+        <v>18690</v>
       </c>
       <c r="L13" t="n">
-        <v>262500</v>
+        <v>18760</v>
       </c>
       <c r="M13" t="n">
-        <v>249500</v>
+        <v>17910</v>
       </c>
       <c r="N13" t="n">
-        <v>46.38</v>
+        <v>27.68</v>
       </c>
       <c r="O13" t="n">
-        <v>3949715047750</v>
+        <v>66823712780</v>
       </c>
       <c r="P13" t="n">
-        <v>374500</v>
+        <v>35350</v>
       </c>
       <c r="Q13" t="n">
-        <v>90200</v>
+        <v>17910</v>
       </c>
       <c r="R13" t="n">
-        <v>-1572000</v>
+        <v>93000</v>
       </c>
       <c r="S13" t="n">
-        <v>-583000</v>
+        <v>23000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>정부 정책 실패 및 시스템 문제로 인한 증시 전반의 불안 심리. 삼성전자 주가 하락에 대한 부정적 전망.</t>
+          <t>역대 최대 실적에도 불구하고 주가 신저가 기록. 공매도 및 시장 불안정성에 대한 불만 제기.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['정부 정책', '증시 불안', '주가 하락']</t>
+          <t>['실적', '주가 신저가', '공매도']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17970</v>
+        <v>1605000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-4.72%</t>
+          <t>'-4.52%</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>152</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>78</v>
+        <v>493</v>
       </c>
       <c r="G14" t="n">
-        <v>440</v>
+        <v>1987</v>
       </c>
       <c r="H14" t="n">
-        <v>27.61</v>
+        <v>49.52</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18860</v>
+        <v>1681000</v>
       </c>
       <c r="K14" t="n">
-        <v>18690</v>
+        <v>1640000</v>
       </c>
       <c r="L14" t="n">
-        <v>18760</v>
+        <v>1653000</v>
       </c>
       <c r="M14" t="n">
-        <v>17910</v>
+        <v>1605000</v>
       </c>
       <c r="N14" t="n">
-        <v>27.68</v>
+        <v>49.59</v>
       </c>
       <c r="O14" t="n">
-        <v>62769427650</v>
+        <v>4768109429500</v>
       </c>
       <c r="P14" t="n">
-        <v>35350</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>17910</v>
+        <v>403000</v>
       </c>
       <c r="R14" t="n">
-        <v>93000</v>
+        <v>-259000</v>
       </c>
       <c r="S14" t="n">
-        <v>23000</v>
+        <v>88000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>실적 호조에도 불구하고 주가 하락 및 52주 신저가 기록. 공매도 관련 불만과 조선업 전반의 부정적 전망.</t>
+          <t>정부 정책 및 시장 상황으로 인한 주가 하락 우려. 기업 실적 대비 주가 부진 및 시장 불신 표출.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['실적', '공매도', '신저가']</t>
+          <t>['주가 하락', '시장 불신', '기업 실적']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7770</v>
+        <v>7760</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-4.78%</t>
+          <t>'-4.90%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F15" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G15" t="n">
-        <v>827</v>
+        <v>837</v>
       </c>
       <c r="H15" t="n">
         <v>26.37</v>
@@ -1806,7 +1806,7 @@
         <v>26.38</v>
       </c>
       <c r="O15" t="n">
-        <v>31216704715</v>
+        <v>32002195195</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1855,24 +1855,24 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15730</v>
+        <v>15720</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-7.31%</t>
+          <t>'-7.37%</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>-0.6</v>
       </c>
       <c r="E16" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="F16" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G16" t="n">
-        <v>603</v>
+        <v>610</v>
       </c>
       <c r="H16" t="n">
         <v>3.37</v>
@@ -1898,7 +1898,7 @@
         <v>3.97</v>
       </c>
       <c r="O16" t="n">
-        <v>85067594480</v>
+        <v>85651828280</v>
       </c>
       <c r="P16" t="n">
         <v>31500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>AI 및 광통신 테마 확산 속 대한광통신 3분기 어닝 서프라이즈 기록. 공매도 규제 논의.</t>
+          <t>3분기 어닝 서프라이즈 기록. AI 및 광통신 테마 성장 가능성 및 공매도 규제 관련 기대감.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['대한광통신', '어닝 서프라이즈', 'AI 테마']</t>
+          <t>['어닝 서프라이즈', '광통신 테마', '공매도 규제']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25750</v>
+        <v>25700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'-8.36%</t>
+          <t>'-8.54%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.5600000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F17" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G17" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H17" t="n">
         <v>9.460000000000001</v>
@@ -1990,7 +1990,7 @@
         <v>10.02</v>
       </c>
       <c r="O17" t="n">
-        <v>68487984000</v>
+        <v>69737800700</v>
       </c>
       <c r="P17" t="n">
         <v>75900</v>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10390</v>
+        <v>10350</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'-8.38%</t>
+          <t>'-8.73%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F18" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G18" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="H18" t="n">
         <v>0.41</v>
@@ -2082,7 +2082,7 @@
         <v>0.44</v>
       </c>
       <c r="O18" t="n">
-        <v>32113397130</v>
+        <v>32202634830</v>
       </c>
       <c r="P18" t="n">
         <v>29750</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3845</v>
+        <v>3895</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-9.95%</t>
+          <t>'-8.78%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-2.94</v>
       </c>
       <c r="E19" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F19" t="n">
         <v>32</v>
       </c>
       <c r="G19" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H19" t="n">
         <v>1.52</v>
@@ -2174,7 +2174,7 @@
         <v>4.46</v>
       </c>
       <c r="O19" t="n">
-        <v>19535483868</v>
+        <v>19615023663</v>
       </c>
       <c r="P19" t="n">
         <v>5470</v>

--- a/data/trending_integrated_20261012_15.xlsx
+++ b/data/trending_integrated_20261012_15.xlsx
@@ -578,10 +578,10 @@
         <v>0.61</v>
       </c>
       <c r="E2" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G2" t="n">
         <v>284</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19991877220</v>
+        <v>19994919220</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -670,13 +670,13 @@
         <v>0.91</v>
       </c>
       <c r="E3" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G3" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>132412598390</v>
+        <v>132414668480</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -762,13 +762,13 @@
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="F4" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G4" t="n">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>188731428075</v>
+        <v>188776465475</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -854,13 +854,13 @@
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F5" t="n">
         <v>33</v>
       </c>
       <c r="G5" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>11917846345</v>
+        <v>11919080341</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -946,13 +946,13 @@
         <v>-1.1</v>
       </c>
       <c r="E6" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F6" t="n">
         <v>91</v>
       </c>
       <c r="G6" t="n">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="H6" t="n">
         <v>1.99</v>
@@ -978,7 +978,7 @@
         <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>128837865555</v>
+        <v>128876842155</v>
       </c>
       <c r="P6" t="n">
         <v>23500</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>건설기초소재 관련 긍정적 전망과 공매도 관련 언급. 주가 상승에 대한 기대감.</t>
+          <t>성수 메가프로젝트 등 건설 관련 호재 기반의 긍정적 전망 및 공매도 세력에 대한 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['건설', '공매도', '전망']</t>
+          <t>['성수 메가프로젝트', '건설 기초 소재', '공매도']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,7 +1038,7 @@
         <v>0.16</v>
       </c>
       <c r="E7" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F7" t="n">
         <v>47</v>
@@ -1070,7 +1070,7 @@
         <v>1.32</v>
       </c>
       <c r="O7" t="n">
-        <v>36133860005</v>
+        <v>36145670075</v>
       </c>
       <c r="P7" t="n">
         <v>2465</v>
@@ -1130,13 +1130,13 @@
         <v>-1.19</v>
       </c>
       <c r="E8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="n">
         <v>52</v>
       </c>
       <c r="G8" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H8" t="n">
         <v>0.78</v>
@@ -1162,7 +1162,7 @@
         <v>1.97</v>
       </c>
       <c r="O8" t="n">
-        <v>74188177931</v>
+        <v>74190737831</v>
       </c>
       <c r="P8" t="n">
         <v>6660</v>
@@ -1222,13 +1222,13 @@
         <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="F9" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G9" t="n">
-        <v>3169</v>
+        <v>3192</v>
       </c>
       <c r="H9" t="n">
         <v>13.33</v>
@@ -1314,13 +1314,13 @@
         <v>0.01</v>
       </c>
       <c r="E10" t="n">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="F10" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G10" t="n">
-        <v>901</v>
+        <v>918</v>
       </c>
       <c r="H10" t="n">
         <v>9.470000000000001</v>
@@ -1346,7 +1346,7 @@
         <v>9.460000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>66968904280</v>
+        <v>66983208290</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1406,13 +1406,13 @@
         <v>0.12</v>
       </c>
       <c r="E11" t="n">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="F11" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="G11" t="n">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="H11" t="n">
         <v>0.21</v>
@@ -1438,7 +1438,7 @@
         <v>0.09</v>
       </c>
       <c r="O11" t="n">
-        <v>162469029550</v>
+        <v>162484276720</v>
       </c>
       <c r="P11" t="n">
         <v>28700</v>
@@ -1501,10 +1501,10 @@
         <v>800</v>
       </c>
       <c r="F12" t="n">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="G12" t="n">
-        <v>2003</v>
+        <v>2042</v>
       </c>
       <c r="H12" t="n">
         <v>46.35</v>
@@ -1530,7 +1530,7 @@
         <v>46.38</v>
       </c>
       <c r="O12" t="n">
-        <v>4361609191750</v>
+        <v>4362878224750</v>
       </c>
       <c r="P12" t="n">
         <v>374500</v>
@@ -1546,16 +1546,16 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정부 정책 및 거시 경제 상황에 대한 불만 고조. 시장 시스템 및 한국 증시의 이상 징후 제기.</t>
+          <t>정부 정책 실패로 인한 국내 증시 전반의 불안정 심화 및 삼성전자 주가 하락에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['정부 정책', '거시 경제', '한국 증시']</t>
+          <t>['정부 정책', '국내 증시', '삼성전자']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1590,13 +1590,13 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F13" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G13" t="n">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="H13" t="n">
         <v>27.61</v>
@@ -1622,7 +1622,7 @@
         <v>27.68</v>
       </c>
       <c r="O13" t="n">
-        <v>66823712780</v>
+        <v>66825441740</v>
       </c>
       <c r="P13" t="n">
         <v>35350</v>
@@ -1638,16 +1638,16 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>역대 최대 실적에도 불구하고 주가 신저가 기록. 공매도 및 시장 불안정성에 대한 불만 제기.</t>
+          <t>역대 최대 실적에도 불구하고 주가 신저가 기록, 조선업 전반에 대한 불안감 및 정부 정책 비판.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['실적', '주가 신저가', '공매도']</t>
+          <t>['역대 최대 실적', '주가 신저가', '조선업']</t>
         </is>
       </c>
       <c r="X13" t="n">
@@ -1685,10 +1685,10 @@
         <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="G14" t="n">
-        <v>1987</v>
+        <v>2020</v>
       </c>
       <c r="H14" t="n">
         <v>49.52</v>
@@ -1714,7 +1714,7 @@
         <v>49.59</v>
       </c>
       <c r="O14" t="n">
-        <v>4768109429500</v>
+        <v>4768143134500</v>
       </c>
       <c r="P14" t="n">
         <v>2987000</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>정부 정책 및 시장 상황으로 인한 주가 하락 우려. 기업 실적 대비 주가 부진 및 시장 불신 표출.</t>
+          <t>정부 정책 실패로 인한 국내 증시 불신 심화 및 SK하이닉스 주가 폭락에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,7 +1739,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가 하락', '시장 불신', '기업 실적']</t>
+          <t>['국내 증시 불신', '주가 폭락', 'SK하이닉스']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1774,13 +1774,13 @@
         <v>-0.01</v>
       </c>
       <c r="E15" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F15" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G15" t="n">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="H15" t="n">
         <v>26.37</v>
@@ -1806,7 +1806,7 @@
         <v>26.38</v>
       </c>
       <c r="O15" t="n">
-        <v>32002195195</v>
+        <v>32004895675</v>
       </c>
       <c r="P15" t="n">
         <v>17950</v>
@@ -1866,13 +1866,13 @@
         <v>-0.6</v>
       </c>
       <c r="E16" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F16" t="n">
         <v>86</v>
       </c>
       <c r="G16" t="n">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="H16" t="n">
         <v>3.37</v>
@@ -1898,7 +1898,7 @@
         <v>3.97</v>
       </c>
       <c r="O16" t="n">
-        <v>85651828280</v>
+        <v>85711831520</v>
       </c>
       <c r="P16" t="n">
         <v>31500</v>
@@ -1958,13 +1958,13 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F17" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G17" t="n">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="H17" t="n">
         <v>9.460000000000001</v>
@@ -1990,7 +1990,7 @@
         <v>10.02</v>
       </c>
       <c r="O17" t="n">
-        <v>69737800700</v>
+        <v>69814926400</v>
       </c>
       <c r="P17" t="n">
         <v>75900</v>
@@ -2050,10 +2050,10 @@
         <v>-0.03</v>
       </c>
       <c r="E18" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F18" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G18" t="n">
         <v>131</v>
@@ -2082,7 +2082,7 @@
         <v>0.44</v>
       </c>
       <c r="O18" t="n">
-        <v>32202634830</v>
+        <v>32209548630</v>
       </c>
       <c r="P18" t="n">
         <v>29750</v>
@@ -2148,7 +2148,7 @@
         <v>32</v>
       </c>
       <c r="G19" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H19" t="n">
         <v>1.52</v>
@@ -2174,7 +2174,7 @@
         <v>4.46</v>
       </c>
       <c r="O19" t="n">
-        <v>19615023663</v>
+        <v>19621099863</v>
       </c>
       <c r="P19" t="n">
         <v>5470</v>
